--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD52516A-4DD5-46A9-835F-52AE62BC8803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F8CDCC-7E34-456C-815A-F5BAC669EAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
     <sheet name="Agustus" sheetId="2" r:id="rId2"/>
+    <sheet name="September" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="218">
   <si>
     <t>REKAP TAHIGAN PEKERJAAN</t>
   </si>
@@ -542,6 +543,153 @@
   </si>
   <si>
     <t>NSS</t>
+  </si>
+  <si>
+    <t>Perbaikan Komputer</t>
+  </si>
+  <si>
+    <t>6 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Pa Dosen</t>
+  </si>
+  <si>
+    <t>Bos Obeng</t>
+  </si>
+  <si>
+    <t>Service Cuci AC</t>
+  </si>
+  <si>
+    <t>7 Agustus 2026</t>
+  </si>
+  <si>
+    <t>10 Agustus 2026</t>
+  </si>
+  <si>
+    <t>11 Agustus 2026</t>
+  </si>
+  <si>
+    <t>12 Agustus 2026</t>
+  </si>
+  <si>
+    <t>13 Agustus 2026</t>
+  </si>
+  <si>
+    <t>15 Agustus 2026</t>
+  </si>
+  <si>
+    <t>18 Agustus 2026</t>
+  </si>
+  <si>
+    <t>19 Agustus 2026</t>
+  </si>
+  <si>
+    <t>21 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Mesjid Muhammadiyah</t>
+  </si>
+  <si>
+    <t>22 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Mtsn 4 Tabalong</t>
+  </si>
+  <si>
+    <t>Paket Ezviz H6C + Pasang TV</t>
+  </si>
+  <si>
+    <t>Ocretta Coffe</t>
+  </si>
+  <si>
+    <t>23 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Zuhri</t>
+  </si>
+  <si>
+    <t>Paket Ezviz</t>
+  </si>
+  <si>
+    <t>Paket Hikvision</t>
+  </si>
+  <si>
+    <t>25 Agustus 2026</t>
+  </si>
+  <si>
+    <t>26 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Pangkalan Agung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H Hasan </t>
+  </si>
+  <si>
+    <t>27 Agustus 2026</t>
+  </si>
+  <si>
+    <t>SMA 1 Tanjung</t>
+  </si>
+  <si>
+    <t>Pasang Kipas Celling</t>
+  </si>
+  <si>
+    <t>H Jani</t>
+  </si>
+  <si>
+    <t>Pasang dan Reposisi CCTV</t>
+  </si>
+  <si>
+    <t>H Mustofa</t>
+  </si>
+  <si>
+    <t>30 Agustus 2026</t>
+  </si>
+  <si>
+    <t>Ibu Guru An-Nahl (Mahligai)</t>
+  </si>
+  <si>
+    <t>Reposisi Kamera Ezviz</t>
+  </si>
+  <si>
+    <t>Mbg Polres</t>
+  </si>
+  <si>
+    <t>Pasang CCTV Baru</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>29 Agustus 2026</t>
+  </si>
+  <si>
+    <t>SDN 2 Agung</t>
+  </si>
+  <si>
+    <t>Toko Azizah</t>
+  </si>
+  <si>
+    <t>REKAP TAGIHAN PEKERJAAN</t>
+  </si>
+  <si>
+    <t>01 September 2026</t>
+  </si>
+  <si>
+    <t>Pemasangan Ruijie</t>
+  </si>
+  <si>
+    <t>Pa Dewan</t>
+  </si>
+  <si>
+    <t>Harddisk 4TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandi </t>
+  </si>
+  <si>
+    <t>Pengambilan Ezviz H6c Pro 2k (5 Unit)</t>
   </si>
 </sst>
 </file>
@@ -672,7 +820,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2307,13 +2476,13 @@
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H59">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="DIBAYAR">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="DITAGIH">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="DITAGIH">
       <formula>NOT(ISERROR(SEARCH("DITAGIH",H5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="DIBUAT">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="DIBUAT">
       <formula>NOT(ISERROR(SEARCH("DIBUAT",H5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2331,7 +2500,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867879EA-6F57-4527-BD9D-B58F88ECFB1A}">
-  <dimension ref="B2:Q60"/>
+  <dimension ref="B2:Q70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2469,8 +2638,12 @@
       <c r="Q6" s="7"/>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B7" s="15"/>
-      <c r="C7" s="5"/>
+      <c r="B7" s="15">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="D7" s="5"/>
       <c r="E7" s="4" t="s">
         <v>115</v>
@@ -2525,12 +2698,8 @@
       <c r="Q8" s="7"/>
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B9" s="15">
-        <v>2</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>116</v>
-      </c>
+      <c r="B9" s="15"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="4" t="s">
         <v>117</v>
@@ -2839,20 +3008,24 @@
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="15"/>
-      <c r="C25" s="5"/>
+      <c r="B25" s="15">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>170</v>
+      </c>
       <c r="D25" s="5"/>
       <c r="E25" s="4" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="G25" s="6">
-        <v>2625000</v>
+        <v>100000</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -2862,13 +3035,13 @@
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="4" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="G26" s="6">
-        <v>300000</v>
+        <v>200000</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>13</v>
@@ -2877,17 +3050,21 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="15"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="15">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="D27" s="5"/>
       <c r="E27" s="4" t="s">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="G27" s="6">
-        <v>4630000</v>
+        <v>1947500</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>13</v>
@@ -2896,20 +3073,24 @@
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="15"/>
-      <c r="C28" s="5"/>
+      <c r="B28" s="15">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>175</v>
+      </c>
       <c r="D28" s="5"/>
       <c r="E28" s="4" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G28" s="6">
-        <v>756000</v>
+        <v>2625000</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -2919,35 +3100,39 @@
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="4" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="G29" s="6">
-        <v>1600000</v>
+        <v>100000</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="15"/>
-      <c r="C30" s="5"/>
+      <c r="B30" s="15">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>176</v>
+      </c>
       <c r="D30" s="5"/>
       <c r="E30" s="4" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G30" s="6">
-        <v>382000</v>
+        <v>300000</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -2957,13 +3142,13 @@
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="4" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="G31" s="6">
-        <v>490000</v>
+        <v>4630000</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>13</v>
@@ -2976,13 +3161,13 @@
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="G32" s="6">
-        <v>350000</v>
+        <v>756000</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>13</v>
@@ -2991,39 +3176,47 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="15"/>
-      <c r="C33" s="5"/>
+      <c r="B33" s="15">
+        <v>7</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="D33" s="5"/>
       <c r="E33" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>158</v>
+        <v>125</v>
       </c>
       <c r="G33" s="6">
-        <v>440000</v>
+        <v>1600000</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="15"/>
-      <c r="C34" s="5"/>
+      <c r="B34" s="15">
+        <v>8</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>178</v>
+      </c>
       <c r="D34" s="5"/>
       <c r="E34" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="G34" s="6">
-        <v>75000</v>
+        <v>382000</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -3033,35 +3226,39 @@
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="4" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="G35" s="6">
-        <v>300000</v>
+        <v>490000</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="15"/>
-      <c r="C36" s="5"/>
+      <c r="B36" s="15">
+        <v>9</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="D36" s="5"/>
       <c r="E36" s="4" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>120</v>
       </c>
       <c r="G36" s="6">
-        <v>150000</v>
+        <v>350000</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -3071,13 +3268,13 @@
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G37" s="6">
-        <v>250000</v>
+        <v>440000</v>
       </c>
       <c r="H37" s="4" t="s">
         <v>13</v>
@@ -3090,16 +3287,16 @@
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G38" s="6">
-        <v>415000</v>
+        <v>75000</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -3109,7 +3306,7 @@
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="4" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>120</v>
@@ -3128,13 +3325,13 @@
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>120</v>
       </c>
       <c r="G40" s="6">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>103</v>
@@ -3143,7 +3340,1108 @@
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="15"/>
+      <c r="B41" s="15">
+        <v>10</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G41" s="6">
+        <v>250000</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="15"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G42" s="6">
+        <v>415000</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="15">
+        <v>11</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="E43" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G43" s="6">
+        <v>300000</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="15">
+        <v>12</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" s="6">
+        <v>715000</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="15">
+        <v>13</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="E45" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="G45" s="6">
+        <v>3750000</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="15">
+        <v>14</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D46" s="5"/>
+      <c r="E46" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G46" s="6">
+        <v>2400000</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="15"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="G47" s="6">
+        <v>8650000</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="15">
+        <v>15</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G48" s="6">
+        <v>200000</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="15"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="G49" s="6">
+        <v>100000</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="15">
+        <v>16</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D50" s="5"/>
+      <c r="E50" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G50" s="6">
+        <v>225000</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="15"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G51" s="6">
+        <v>200000</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="15"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G52" s="6">
+        <v>600000</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="15">
+        <v>17</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="G53" s="6">
+        <v>835000</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="15">
+        <v>18</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G54" s="6">
+        <v>4575000</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="15"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G55" s="6">
+        <v>130000</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="15"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G56" s="6">
+        <v>500000</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="15"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G57" s="6">
+        <v>5165000</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="15">
+        <v>19</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="D58" s="5"/>
+      <c r="E58" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G58" s="6">
+        <v>300000</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="15"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="15"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="15"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="15"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="15"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="15"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="15"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="15"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" s="15"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="15"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" s="15"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G70" s="16">
+        <f>SUM(G5:G69)</f>
+        <v>115616500</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H5:H69">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="DIBAYAR">
+      <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="DITAGIH">
+      <formula>NOT(ISERROR(SEARCH("DITAGIH",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="DIBUAT">
+      <formula>NOT(ISERROR(SEARCH("DIBUAT",H5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I69" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
+      <formula1>"TUNAI,TRANSFER"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H69" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
+      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{921572B4-6C20-499B-A19B-2B4CE7B2EFBB}">
+  <dimension ref="B2:Q70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="74.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" style="3" customWidth="1"/>
+    <col min="8" max="9" width="22" style="1" customWidth="1"/>
+    <col min="10" max="10" width="51.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="3.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="1.42578125" style="1" customWidth="1"/>
+    <col min="15" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="3.5703125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+    </row>
+    <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="15">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="6">
+        <v>450000</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="G6" s="6">
+        <v>2850000</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B8" s="15"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="15"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="15"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="15"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="15"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="15"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="15"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="15"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="15"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="15"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="15"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="15"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="15">
+        <v>3</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="15">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="15">
+        <v>5</v>
+      </c>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="15"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="15">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="15"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="15"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="4"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="15">
+        <v>7</v>
+      </c>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="4"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="15">
+        <v>8</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="4"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="15"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="15">
+        <v>9</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="4"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="15"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="15"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="4"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="15"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="15"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="4"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="15">
+        <v>10</v>
+      </c>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="4"/>
@@ -3165,7 +4463,9 @@
       <c r="J42" s="4"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="15"/>
+      <c r="B43" s="15">
+        <v>11</v>
+      </c>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="4"/>
@@ -3176,7 +4476,9 @@
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="15"/>
+      <c r="B44" s="15">
+        <v>12</v>
+      </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="4"/>
@@ -3187,7 +4489,9 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="15"/>
+      <c r="B45" s="15">
+        <v>13</v>
+      </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="4"/>
@@ -3198,7 +4502,9 @@
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="15"/>
+      <c r="B46" s="15">
+        <v>14</v>
+      </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="4"/>
@@ -3220,7 +4526,9 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="15"/>
+      <c r="B48" s="15">
+        <v>15</v>
+      </c>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="4"/>
@@ -3242,7 +4550,9 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="15"/>
+      <c r="B50" s="15">
+        <v>16</v>
+      </c>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="4"/>
@@ -3275,7 +4585,9 @@
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="15"/>
+      <c r="B53" s="15">
+        <v>17</v>
+      </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="4"/>
@@ -3286,7 +4598,9 @@
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="15"/>
+      <c r="B54" s="15">
+        <v>18</v>
+      </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="4"/>
@@ -3330,7 +4644,9 @@
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="15"/>
+      <c r="B58" s="15">
+        <v>19</v>
+      </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="4"/>
@@ -3344,17 +4660,133 @@
       <c r="B59" s="15"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="6"/>
+      <c r="E59" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>207</v>
+      </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G60" s="16">
-        <f>SUM(G5:G59)</f>
-        <v>85124000</v>
+      <c r="B60" s="15"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="15"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="15"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="15"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="15"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="15"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="15"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" s="15"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="15"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" s="15"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G70" s="16">
+        <f>SUM(G5:G69)</f>
+        <v>3300000</v>
       </c>
     </row>
   </sheetData>
@@ -3362,7 +4794,7 @@
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H59">
+  <conditionalFormatting sqref="H5:H69">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
@@ -3374,11 +4806,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I59" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H69" xr:uid="{D40D73DF-17D8-4369-B0DF-04510FA59EB8}">
+      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I69" xr:uid="{B03ED550-A901-4976-BC2F-1D6468F9DB7D}">
       <formula1>"TUNAI,TRANSFER"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H59" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
-      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F8CDCC-7E34-456C-815A-F5BAC669EAEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A360B8-C3D2-4033-8A8F-260771BD1EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="230">
   <si>
     <t>REKAP TAHIGAN PEKERJAAN</t>
   </si>
@@ -690,6 +690,42 @@
   </si>
   <si>
     <t>Pengambilan Ezviz H6c Pro 2k (5 Unit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>02 September  2026</t>
+  </si>
+  <si>
+    <t>Didi Muara Uya</t>
+  </si>
+  <si>
+    <t>PC Kasir &amp; Starlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDN Kalahang </t>
+  </si>
+  <si>
+    <t>Paket 4 Kamera Hillok Standard</t>
+  </si>
+  <si>
+    <t>Aufamart</t>
+  </si>
+  <si>
+    <t>Pasang Ezviz(cahaya) &amp; Perbaikan</t>
+  </si>
+  <si>
+    <t>SDN Maburai</t>
+  </si>
+  <si>
+    <t>Pasang Kamera Baru 3 Unit</t>
+  </si>
+  <si>
+    <t>04 September 2026</t>
+  </si>
+  <si>
+    <t>SDN 2 Tanjung</t>
   </si>
 </sst>
 </file>
@@ -3890,7 +3926,7 @@
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="39.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="1" customWidth="1"/>
     <col min="6" max="6" width="74.7109375" style="1" customWidth="1"/>
@@ -3963,7 +3999,9 @@
       <c r="C5" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>218</v>
+      </c>
       <c r="E5" s="4" t="s">
         <v>111</v>
       </c>
@@ -4051,12 +4089,22 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="15"/>
-      <c r="C8" s="5"/>
+      <c r="C8" s="5" t="s">
+        <v>219</v>
+      </c>
       <c r="D8" s="5"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G8" s="6">
+        <v>12450000</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="L8" s="7"/>
@@ -4070,10 +4118,18 @@
       <c r="B9" s="15"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G9" s="6">
+        <v>4280000</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>103</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="L9" s="7"/>
@@ -4087,10 +4143,18 @@
       <c r="B10" s="15"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="G10" s="6">
+        <v>275000</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
@@ -4098,21 +4162,39 @@
       <c r="B11" s="15"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="G11" s="6">
+        <v>3447000</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="15"/>
-      <c r="C12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>228</v>
+      </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="4"/>
+      <c r="E12" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="6">
+        <v>250000</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
@@ -4786,7 +4868,7 @@
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G70" s="16">
         <f>SUM(G5:G69)</f>
-        <v>3300000</v>
+        <v>24002000</v>
       </c>
     </row>
   </sheetData>

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A360B8-C3D2-4033-8A8F-260771BD1EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6D16B3-375C-45C1-94CC-7B5A7168C061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="598" activeTab="2" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,10 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="230">
-  <si>
-    <t>REKAP TAHIGAN PEKERJAAN</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="250">
   <si>
     <t>No</t>
   </si>
@@ -554,9 +553,6 @@
     <t>Pa Dosen</t>
   </si>
   <si>
-    <t>Bos Obeng</t>
-  </si>
-  <si>
     <t>Service Cuci AC</t>
   </si>
   <si>
@@ -680,15 +676,9 @@
     <t>Pemasangan Ruijie</t>
   </si>
   <si>
-    <t>Pa Dewan</t>
-  </si>
-  <si>
     <t>Harddisk 4TB</t>
   </si>
   <si>
-    <t xml:space="preserve">Sandi </t>
-  </si>
-  <si>
     <t>Pengambilan Ezviz H6c Pro 2k (5 Unit)</t>
   </si>
   <si>
@@ -726,6 +716,78 @@
   </si>
   <si>
     <t>SDN 2 Tanjung</t>
+  </si>
+  <si>
+    <t>Pa Dewan ulah</t>
+  </si>
+  <si>
+    <t>07 September 2026</t>
+  </si>
+  <si>
+    <t>J&amp;T Cargo Sulingan</t>
+  </si>
+  <si>
+    <t>Pasang Baru 2 Kamera</t>
+  </si>
+  <si>
+    <t>Starlink 2 Unit</t>
+  </si>
+  <si>
+    <t>Tanjung Putra</t>
+  </si>
+  <si>
+    <t>Perbaikan AC,CCTV,Listrik,dll</t>
+  </si>
+  <si>
+    <t>PT Mizan</t>
+  </si>
+  <si>
+    <t>08 September 2026</t>
+  </si>
+  <si>
+    <t>Ibu Nia</t>
+  </si>
+  <si>
+    <t>1 Paket Ezviz TY1 Pro 3mp + Memori 32GB</t>
+  </si>
+  <si>
+    <t>SSD NVME Visipro Turbo 1TB</t>
+  </si>
+  <si>
+    <t>Ari Oche</t>
+  </si>
+  <si>
+    <t>Instalasi Kasir,Kamera dan Jaringan</t>
+  </si>
+  <si>
+    <t>Sekolah Alam</t>
+  </si>
+  <si>
+    <t>Setting Ulang</t>
+  </si>
+  <si>
+    <t>Pa Udin</t>
+  </si>
+  <si>
+    <t>Pasang Ezviz</t>
+  </si>
+  <si>
+    <t>09 September 2026</t>
+  </si>
+  <si>
+    <t>PT AMP Kasiau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reposisi Kamera </t>
+  </si>
+  <si>
+    <t>SDN Banua Rantau</t>
+  </si>
+  <si>
+    <t>3 Paket Imou Ranger 2</t>
+  </si>
+  <si>
+    <t>Pa Husein</t>
   </si>
 </sst>
 </file>
@@ -735,7 +797,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -764,8 +826,15 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -781,6 +850,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,7 +887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -846,6 +921,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1231,7 +1313,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D327584B-2C7E-47E2-A46B-99BF2D9CC958}">
   <dimension ref="B2:Q60"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
@@ -1252,90 +1334,90 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
+      <c r="B2" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
     </row>
     <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>5</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>19</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="G5" s="6">
         <v>15000000</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
@@ -1345,34 +1427,34 @@
         <v>2</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G6" s="6">
         <v>8250000</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
@@ -1382,32 +1464,32 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="G7" s="6">
         <v>3185000</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
@@ -1417,20 +1499,20 @@
         <v>4</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="G8" s="6">
         <v>7501000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -1446,20 +1528,20 @@
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" s="6">
         <v>9790000</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1469,20 +1551,20 @@
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="5"/>
       <c r="E10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="G10" s="6">
         <v>303000</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -1492,20 +1574,20 @@
         <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" s="6">
         <v>250000</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -1515,20 +1597,20 @@
         <v>8</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="G12" s="6">
         <v>3892000</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1538,20 +1620,20 @@
         <v>9</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="G13" s="6">
         <v>800000</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1561,20 +1643,20 @@
         <v>10</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="G14" s="6">
         <v>1792000</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -1584,20 +1666,20 @@
         <v>11</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" s="6">
         <v>540000</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1607,20 +1689,20 @@
         <v>12</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G16" s="6">
         <v>200000</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -1630,20 +1712,20 @@
         <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="G17" s="6">
         <v>6501000</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
@@ -1653,20 +1735,20 @@
         <v>14</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="6">
         <v>550000</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
@@ -1676,20 +1758,20 @@
         <v>15</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="G19" s="6">
         <v>400000</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -1699,20 +1781,20 @@
         <v>16</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20" s="6">
         <v>645000</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -1722,20 +1804,20 @@
         <v>17</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21" s="6">
         <v>235000</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
@@ -1745,20 +1827,20 @@
         <v>18</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="G22" s="6">
         <v>3045000</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -1768,20 +1850,20 @@
         <v>19</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D23" s="5"/>
       <c r="E23" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" s="6">
         <v>312000</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -1802,20 +1884,20 @@
         <v>21</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="G25" s="6">
         <v>3150000</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1825,20 +1907,20 @@
         <v>22</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="G26" s="6">
         <v>215000</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -1848,20 +1930,20 @@
         <v>23</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>65</v>
       </c>
       <c r="G27" s="6">
         <v>275000</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1871,20 +1953,20 @@
         <v>24</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G28" s="6">
         <v>2605000</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
@@ -1894,20 +1976,20 @@
         <v>25</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="G29" s="6">
         <v>8289000</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
@@ -1917,20 +1999,20 @@
         <v>26</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G30" s="6">
         <v>1550000</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -1940,20 +2022,20 @@
         <v>27</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D31" s="5"/>
       <c r="E31" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>72</v>
       </c>
       <c r="G31" s="6">
         <v>24540000</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -1963,20 +2045,20 @@
         <v>28</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G32" s="6">
         <v>1277000</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -1997,20 +2079,20 @@
         <v>30</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D34" s="5"/>
       <c r="E34" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G34" s="6">
         <v>2425000</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -2022,10 +2104,10 @@
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G35" s="6"/>
       <c r="H35" s="4"/>
@@ -2037,20 +2119,20 @@
         <v>32</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="G36" s="6">
         <v>728000</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -2071,20 +2153,20 @@
         <v>34</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="G38" s="6">
         <v>850000</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -2094,20 +2176,20 @@
         <v>35</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G39" s="6">
         <v>850000</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
@@ -2117,20 +2199,20 @@
         <v>36</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="G40" s="6">
         <v>100000</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -2140,20 +2222,20 @@
         <v>37</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G41" s="6">
         <v>320000</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
@@ -2163,20 +2245,20 @@
         <v>38</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D42" s="5"/>
       <c r="E42" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G42" s="6">
         <v>150000</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
@@ -2186,20 +2268,20 @@
         <v>39</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="G43" s="6">
         <v>400000</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -2209,20 +2291,20 @@
         <v>40</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D44" s="5"/>
       <c r="E44" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G44" s="6">
         <v>1654000</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -2232,20 +2314,20 @@
         <v>41</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G45" s="6">
         <v>225000</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -2255,20 +2337,20 @@
         <v>42</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D46" s="5"/>
       <c r="E46" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="G46" s="6">
         <v>375000</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
@@ -2278,20 +2360,20 @@
         <v>42</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>97</v>
       </c>
       <c r="G47" s="6">
         <v>550000</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
@@ -2301,20 +2383,20 @@
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>98</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>99</v>
       </c>
       <c r="G48" s="6">
         <v>2605000</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
@@ -2324,20 +2406,20 @@
         <v>44</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D49" s="5"/>
       <c r="E49" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G49" s="6">
         <v>36000000</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
@@ -2347,20 +2429,20 @@
         <v>45</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D50" s="5"/>
       <c r="E50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>102</v>
       </c>
       <c r="G50" s="6">
         <v>150000</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -2370,20 +2452,20 @@
         <v>46</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G51" s="6">
         <v>10600000</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
@@ -2393,20 +2475,20 @@
         <v>47</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>106</v>
       </c>
       <c r="G52" s="6">
         <v>800000</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
@@ -2416,20 +2498,20 @@
         <v>48</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>108</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>109</v>
       </c>
       <c r="G53" s="6">
         <v>1260000</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -2536,8 +2618,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867879EA-6F57-4527-BD9D-B58F88ECFB1A}">
-  <dimension ref="B2:Q70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:Q69"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
@@ -2558,86 +2640,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
+      <c r="B2" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
     </row>
     <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>5</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="G5" s="6">
         <v>39194000</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
@@ -2647,28 +2729,28 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="G6" s="6">
         <v>230000</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
@@ -2678,32 +2760,32 @@
         <v>2</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G7" s="6">
         <v>155000</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
@@ -2713,16 +2795,16 @@
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>122</v>
       </c>
       <c r="G8" s="6">
         <v>1200000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -2738,16 +2820,16 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="G9" s="6">
         <v>940000</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -2762,18 +2844,10 @@
       <c r="B10" s="15"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G10" s="6">
-        <v>700000</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
     </row>
@@ -2782,16 +2856,16 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G11" s="6">
         <v>665000</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -2801,16 +2875,16 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="G12" s="6">
         <v>850000</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -2820,16 +2894,16 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13" s="6">
         <v>1600000</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -2839,16 +2913,16 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="G14" s="6">
         <v>17104000</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -2858,16 +2932,16 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="G15" s="6">
         <v>1250000</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -2877,16 +2951,16 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="G16" s="6">
         <v>1135000</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -2896,16 +2970,16 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" s="6">
         <v>300000</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
@@ -2915,16 +2989,16 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G18" s="6">
         <v>1700000</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
@@ -2934,16 +3008,16 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>136</v>
       </c>
       <c r="G19" s="6">
         <v>180000</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -2953,54 +3027,54 @@
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20" s="6">
         <v>185000</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B21" s="15"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="4" t="s">
+    <row r="21" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="G21" s="21">
         <v>155000</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
+      <c r="H21" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" s="6">
         <v>938000</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -3010,16 +3084,16 @@
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" s="6">
         <v>180000</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
@@ -3029,16 +3103,16 @@
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="G24" s="6">
         <v>3200000</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -3048,127 +3122,127 @@
         <v>3</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="G25" s="6">
         <v>100000</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="15"/>
-      <c r="C26" s="5"/>
+      <c r="B26" s="15">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>172</v>
+      </c>
       <c r="D26" s="5"/>
       <c r="E26" s="4" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G26" s="6">
-        <v>200000</v>
+        <v>1947500</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="4" t="s">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="G27" s="6">
-        <v>1947500</v>
+        <v>2625000</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B28" s="15">
-        <v>5</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>175</v>
-      </c>
+      <c r="B28" s="15"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="5"/>
       <c r="E28" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="G28" s="6">
-        <v>2625000</v>
+        <v>100000</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="15"/>
-      <c r="C29" s="5"/>
+      <c r="B29" s="15">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>174</v>
+      </c>
       <c r="D29" s="5"/>
       <c r="E29" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="G29" s="6">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="15">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>176</v>
-      </c>
+      <c r="B30" s="15"/>
+      <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="4" t="s">
         <v>147</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G30" s="6">
-        <v>300000</v>
+        <v>4630000</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -3178,123 +3252,123 @@
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G31" s="6">
-        <v>4630000</v>
+        <v>756000</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="15"/>
-      <c r="C32" s="5"/>
+      <c r="B32" s="15">
+        <v>7</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>175</v>
+      </c>
       <c r="D32" s="5"/>
       <c r="E32" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="G32" s="6">
-        <v>756000</v>
+        <v>1600000</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D33" s="5"/>
       <c r="E33" s="4" t="s">
         <v>153</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="G33" s="6">
-        <v>1600000</v>
+        <v>382000</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="15">
-        <v>8</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>178</v>
-      </c>
+      <c r="B34" s="15"/>
+      <c r="C34" s="5"/>
       <c r="D34" s="5"/>
       <c r="E34" s="4" t="s">
         <v>154</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="G34" s="6">
-        <v>382000</v>
+        <v>490000</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="15"/>
-      <c r="C35" s="5"/>
+      <c r="B35" s="15">
+        <v>9</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="D35" s="5"/>
       <c r="E35" s="4" t="s">
         <v>155</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="G35" s="6">
-        <v>490000</v>
+        <v>350000</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="15">
-        <v>9</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>179</v>
-      </c>
+      <c r="B36" s="15"/>
+      <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="4" t="s">
         <v>156</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="G36" s="6">
-        <v>350000</v>
+        <v>440000</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -3304,16 +3378,16 @@
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G37" s="6">
-        <v>440000</v>
+        <v>75000</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
@@ -3323,16 +3397,16 @@
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="G38" s="6">
-        <v>75000</v>
+        <v>300000</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -3345,104 +3419,108 @@
         <v>161</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G39" s="6">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I39" s="4"/>
       <c r="J39" s="4"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" s="15"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="4" t="s">
+    <row r="40" spans="2:10" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="18">
+        <v>10</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="D40" s="19"/>
+      <c r="E40" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="G40" s="6">
-        <v>150000</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
+      <c r="F40" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G40" s="21">
+        <v>250000</v>
+      </c>
+      <c r="H40" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="15">
-        <v>10</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>180</v>
-      </c>
+      <c r="B41" s="15"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G41" s="6">
-        <v>250000</v>
+        <v>415000</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I41" s="4"/>
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="15"/>
-      <c r="C42" s="5"/>
+      <c r="B42" s="15">
+        <v>11</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>179</v>
+      </c>
       <c r="D42" s="5"/>
       <c r="E42" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="G42" s="6">
-        <v>415000</v>
+        <v>300000</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D43" s="5"/>
       <c r="E43" s="4" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="G43" s="6">
-        <v>300000</v>
+        <v>715000</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>182</v>
@@ -3452,143 +3530,139 @@
         <v>183</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>30</v>
+        <v>184</v>
       </c>
       <c r="G44" s="6">
-        <v>715000</v>
+        <v>3750000</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="4" t="s">
         <v>185</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G45" s="6">
-        <v>3750000</v>
+        <v>2400000</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="15">
-        <v>14</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>188</v>
-      </c>
+      <c r="B46" s="15"/>
+      <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="4" t="s">
         <v>187</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G46" s="6">
-        <v>2400000</v>
+        <v>8650000</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="15"/>
-      <c r="C47" s="5"/>
+      <c r="B47" s="15">
+        <v>15</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="D47" s="5"/>
       <c r="E47" s="4" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>191</v>
+        <v>119</v>
       </c>
       <c r="G47" s="6">
-        <v>8650000</v>
+        <v>200000</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="15">
-        <v>15</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>192</v>
-      </c>
+      <c r="B48" s="15"/>
+      <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="G48" s="6">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="15"/>
-      <c r="C49" s="5"/>
+      <c r="B49" s="15">
+        <v>16</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>191</v>
+      </c>
       <c r="D49" s="5"/>
       <c r="E49" s="4" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="G49" s="6">
-        <v>100000</v>
+        <v>225000</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="15">
-        <v>16</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>193</v>
-      </c>
+      <c r="B50" s="15"/>
+      <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>30</v>
+        <v>171</v>
       </c>
       <c r="G50" s="6">
-        <v>225000</v>
+        <v>200000</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
@@ -3598,45 +3672,49 @@
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="4" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G51" s="6">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="15"/>
-      <c r="C52" s="5"/>
+      <c r="B52" s="15">
+        <v>17</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>194</v>
+      </c>
       <c r="D52" s="5"/>
       <c r="E52" s="4" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="G52" s="6">
-        <v>600000</v>
+        <v>835000</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>103</v>
+        <v>22</v>
       </c>
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="4" t="s">
@@ -3646,33 +3724,29 @@
         <v>198</v>
       </c>
       <c r="G53" s="6">
-        <v>835000</v>
+        <v>4575000</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="15">
-        <v>18</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>208</v>
-      </c>
+      <c r="B54" s="15"/>
+      <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="4" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G54" s="6">
-        <v>4575000</v>
+        <v>130000</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
@@ -3682,16 +3756,16 @@
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>204</v>
+        <v>29</v>
       </c>
       <c r="G55" s="6">
-        <v>130000</v>
+        <v>500000</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
@@ -3701,46 +3775,46 @@
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="4" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>30</v>
+        <v>198</v>
       </c>
       <c r="G56" s="6">
-        <v>500000</v>
+        <v>5165000</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="15"/>
-      <c r="C57" s="5"/>
+      <c r="B57" s="15">
+        <v>19</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>200</v>
+      </c>
       <c r="D57" s="5"/>
       <c r="E57" s="4" t="s">
         <v>201</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G57" s="6">
-        <v>5165000</v>
+        <v>300000</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="15">
-        <v>19</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>202</v>
-      </c>
+      <c r="B58" s="15"/>
+      <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="4" t="s">
         <v>203</v>
@@ -3749,10 +3823,10 @@
         <v>204</v>
       </c>
       <c r="G58" s="6">
-        <v>300000</v>
+        <v>1255000</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>13</v>
+        <v>102</v>
       </c>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
@@ -3761,15 +3835,9 @@
       <c r="B59" s="15"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>207</v>
-      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="6"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
@@ -3868,34 +3936,23 @@
       <c r="D68" s="5"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="G68" s="6"/>
+      <c r="G68" s="6">
+        <f>SUM(G5:G58)</f>
+        <v>115971500</v>
+      </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B69" s="15"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G70" s="16">
-        <f>SUM(G5:G69)</f>
-        <v>115616500</v>
-      </c>
+      <c r="G69" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H69">
+  <conditionalFormatting sqref="H5:H68">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
@@ -3907,10 +3964,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I69" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I68" xr:uid="{8D463466-EF54-4372-8845-E37C7920DA1D}">
       <formula1>"TUNAI,TRANSFER"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H69" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H68" xr:uid="{1B647AD2-72F7-4B88-B373-83AD8FAE4C47}">
       <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3921,8 +3978,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{921572B4-6C20-499B-A19B-2B4CE7B2EFBB}">
-  <dimension ref="B2:Q70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:Q71"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
@@ -3943,88 +4000,88 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="18"/>
+      <c r="B2" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
     </row>
     <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="D4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>5</v>
-      </c>
       <c r="H4" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G5" s="6">
         <v>450000</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="L5" s="7"/>
       <c r="M5" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
@@ -4034,28 +4091,28 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="4" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G6" s="6">
         <v>2850000</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="L6" s="7"/>
       <c r="M6" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
@@ -4065,24 +4122,28 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="4" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="4"/>
+        <v>213</v>
+      </c>
+      <c r="G7" s="6">
+        <v>2250000</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>15</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>16</v>
       </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
@@ -4090,20 +4151,20 @@
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="15"/>
       <c r="C8" s="5" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="G8" s="6">
         <v>12450000</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -4119,16 +4180,16 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="4" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G9" s="6">
         <v>4280000</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -4143,17 +4204,17 @@
       <c r="B10" s="15"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="4" t="s">
-        <v>224</v>
+      <c r="E10" s="17" t="s">
+        <v>220</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G10" s="6">
         <v>275000</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -4163,16 +4224,16 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G11" s="6">
         <v>3447000</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -4180,65 +4241,101 @@
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="15"/>
       <c r="C12" s="5" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12" s="6">
         <v>250000</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
     </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="15"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="4"/>
+      <c r="E13" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G13" s="6">
+        <v>13000000</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="15"/>
-      <c r="C14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>227</v>
+      </c>
       <c r="D14" s="5"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G14" s="6">
+        <v>2800000</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
     </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="15"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G15" s="6">
+        <v>825000</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="15"/>
-      <c r="C16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>234</v>
+      </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G16" s="6">
+        <v>850000</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
     </row>
@@ -4246,21 +4343,39 @@
       <c r="B17" s="15"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="4"/>
+      <c r="E17" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="G17" s="6">
+        <v>3700000</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15"/>
-      <c r="C18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>244</v>
+      </c>
       <c r="D18" s="5"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="4"/>
+      <c r="E18" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G18" s="6">
+        <v>2245000</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
     </row>
@@ -4268,10 +4383,18 @@
       <c r="B19" s="15"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="4"/>
+      <c r="E19" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G19" s="6">
+        <v>100000</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
     </row>
@@ -4279,10 +4402,18 @@
       <c r="B20" s="15"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="4"/>
+      <c r="E20" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G20" s="6">
+        <v>170000</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
     </row>
@@ -4290,10 +4421,18 @@
       <c r="B21" s="15"/>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="4"/>
+      <c r="E21" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1725000</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
     </row>
@@ -4301,10 +4440,18 @@
       <c r="B22" s="15"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="4"/>
+      <c r="E22" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G22" s="6">
+        <v>2250000</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
     </row>
@@ -4312,10 +4459,18 @@
       <c r="B23" s="15"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="4"/>
+      <c r="E23" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="G23" s="6">
+        <v>2250000</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
     </row>
@@ -4331,9 +4486,7 @@
       <c r="J24" s="4"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B25" s="15">
-        <v>3</v>
-      </c>
+      <c r="B25" s="15"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="4"/>
@@ -4344,7 +4497,9 @@
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="15"/>
+      <c r="B26" s="15">
+        <v>3</v>
+      </c>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="4"/>
@@ -4355,9 +4510,7 @@
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="15">
-        <v>4</v>
-      </c>
+      <c r="B27" s="15"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="4"/>
@@ -4369,7 +4522,7 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -4381,7 +4534,9 @@
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="15"/>
+      <c r="B29" s="15">
+        <v>5</v>
+      </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="4"/>
@@ -4392,9 +4547,7 @@
       <c r="J29" s="4"/>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="15">
-        <v>6</v>
-      </c>
+      <c r="B30" s="15"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="4"/>
@@ -4405,7 +4558,9 @@
       <c r="J30" s="4"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="15"/>
+      <c r="B31" s="15">
+        <v>6</v>
+      </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="4"/>
@@ -4427,9 +4582,7 @@
       <c r="J32" s="4"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="15">
-        <v>7</v>
-      </c>
+      <c r="B33" s="15"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="4"/>
@@ -4441,7 +4594,7 @@
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -4453,7 +4606,9 @@
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="15"/>
+      <c r="B35" s="15">
+        <v>8</v>
+      </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="4"/>
@@ -4464,9 +4619,7 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B36" s="15">
-        <v>9</v>
-      </c>
+      <c r="B36" s="15"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="4"/>
@@ -4477,7 +4630,9 @@
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="15"/>
+      <c r="B37" s="15">
+        <v>9</v>
+      </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="4"/>
@@ -4521,9 +4676,7 @@
       <c r="J40" s="4"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" s="15">
-        <v>10</v>
-      </c>
+      <c r="B41" s="15"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="4"/>
@@ -4534,7 +4687,9 @@
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="15"/>
+      <c r="B42" s="15">
+        <v>10</v>
+      </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="4"/>
@@ -4545,9 +4700,7 @@
       <c r="J42" s="4"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B43" s="15">
-        <v>11</v>
-      </c>
+      <c r="B43" s="15"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="4"/>
@@ -4559,7 +4712,7 @@
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -4572,7 +4725,7 @@
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -4585,7 +4738,7 @@
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -4597,7 +4750,9 @@
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="15"/>
+      <c r="B47" s="15">
+        <v>14</v>
+      </c>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="4"/>
@@ -4608,9 +4763,7 @@
       <c r="J47" s="4"/>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="15">
-        <v>15</v>
-      </c>
+      <c r="B48" s="15"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
       <c r="E48" s="4"/>
@@ -4621,7 +4774,9 @@
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="15"/>
+      <c r="B49" s="15">
+        <v>15</v>
+      </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="4"/>
@@ -4632,9 +4787,7 @@
       <c r="J49" s="4"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B50" s="15">
-        <v>16</v>
-      </c>
+      <c r="B50" s="15"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
       <c r="E50" s="4"/>
@@ -4645,7 +4798,9 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="15"/>
+      <c r="B51" s="15">
+        <v>16</v>
+      </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="4"/>
@@ -4667,9 +4822,7 @@
       <c r="J52" s="4"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="15">
-        <v>17</v>
-      </c>
+      <c r="B53" s="15"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
       <c r="E53" s="4"/>
@@ -4681,7 +4834,7 @@
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -4693,7 +4846,9 @@
       <c r="J54" s="4"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55" s="15"/>
+      <c r="B55" s="15">
+        <v>18</v>
+      </c>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="4"/>
@@ -4726,9 +4881,7 @@
       <c r="J57" s="4"/>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="15">
-        <v>19</v>
-      </c>
+      <c r="B58" s="15"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
       <c r="E58" s="4"/>
@@ -4739,18 +4892,14 @@
       <c r="J58" s="4"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="15"/>
+      <c r="B59" s="15">
+        <v>19</v>
+      </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
-      <c r="E59" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>207</v>
-      </c>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="6"/>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
@@ -4759,9 +4908,15 @@
       <c r="B60" s="15"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="6"/>
+      <c r="E60" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>205</v>
+      </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
@@ -4866,9 +5021,20 @@
       <c r="J69" s="4"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G70" s="16">
-        <f>SUM(G5:G69)</f>
-        <v>24002000</v>
+      <c r="B70" s="15"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G71" s="16">
+        <f>SUM(G5:G70)</f>
+        <v>56167000</v>
       </c>
     </row>
   </sheetData>
@@ -4876,7 +5042,8 @@
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H69">
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="H5:H70">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
@@ -4888,10 +5055,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H69" xr:uid="{D40D73DF-17D8-4369-B0DF-04510FA59EB8}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H70" xr:uid="{D40D73DF-17D8-4369-B0DF-04510FA59EB8}">
       <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I69" xr:uid="{B03ED550-A901-4976-BC2F-1D6468F9DB7D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I70" xr:uid="{B03ED550-A901-4976-BC2F-1D6468F9DB7D}">
       <formula1>"TUNAI,TRANSFER"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6D16B3-375C-45C1-94CC-7B5A7168C061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDBFA032-7CBD-4BFB-8C27-F931DBC84DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="598" activeTab="2" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="267">
   <si>
     <t>No</t>
   </si>
@@ -655,9 +655,6 @@
     <t>Pasang CCTV Baru</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>29 Agustus 2026</t>
   </si>
   <si>
@@ -788,6 +785,60 @@
   </si>
   <si>
     <t>Pa Husein</t>
+  </si>
+  <si>
+    <t>Flamboyan (nona hanna tasyia</t>
+  </si>
+  <si>
+    <t>SDN Mabuun</t>
+  </si>
+  <si>
+    <t>SPPG Sulingan</t>
+  </si>
+  <si>
+    <t>Perpusda</t>
+  </si>
+  <si>
+    <t>Perbaikan AC,CCTV,dll</t>
+  </si>
+  <si>
+    <t>10 September 2026</t>
+  </si>
+  <si>
+    <t>11 September 2026</t>
+  </si>
+  <si>
+    <t>13 September 2026</t>
+  </si>
+  <si>
+    <t>14 September 2026</t>
+  </si>
+  <si>
+    <t>Lukbayur</t>
+  </si>
+  <si>
+    <t>4 Paket Ezviz H8c 2mp dan  4mp + Material</t>
+  </si>
+  <si>
+    <t>Setting dan Konfigurasi Ulang</t>
+  </si>
+  <si>
+    <t>Tambah dan Reposisi Kamera</t>
+  </si>
+  <si>
+    <t>Perbaikan,Pergantian,Reposisi Kamera dan Pasang Baru</t>
+  </si>
+  <si>
+    <t>Perbaikan Printer</t>
+  </si>
+  <si>
+    <t>15 September 2026</t>
+  </si>
+  <si>
+    <t>N4 Mart</t>
+  </si>
+  <si>
+    <t>1 Paket Imou PS8E 3mp</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1386,7 @@
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -2641,7 +2692,7 @@
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -3714,7 +3765,7 @@
         <v>18</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="4" t="s">
@@ -3737,7 +3788,7 @@
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>202</v>
@@ -3756,7 +3807,7 @@
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>29</v>
@@ -4001,7 +4052,7 @@
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
       <c r="B2" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C2" s="23"/>
       <c r="D2" s="23"/>
@@ -4054,16 +4105,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>110</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G5" s="6">
         <v>450000</v>
@@ -4091,10 +4142,10 @@
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G6" s="6">
         <v>2850000</v>
@@ -4122,10 +4173,10 @@
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
       <c r="E7" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G7" s="6">
         <v>2250000</v>
@@ -4149,16 +4200,18 @@
       <c r="Q7" s="7"/>
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B8" s="15"/>
+      <c r="B8" s="15">
+        <v>2</v>
+      </c>
       <c r="C8" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>217</v>
       </c>
       <c r="G8" s="6">
         <v>12450000</v>
@@ -4180,10 +4233,10 @@
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>218</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="G9" s="6">
         <v>4280000</v>
@@ -4205,10 +4258,10 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>221</v>
       </c>
       <c r="G10" s="6">
         <v>275000</v>
@@ -4224,10 +4277,10 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="G11" s="6">
         <v>3447000</v>
@@ -4239,13 +4292,15 @@
       <c r="J11" s="4"/>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
+      <c r="B12" s="15">
+        <v>3</v>
+      </c>
       <c r="C12" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>29</v>
@@ -4264,10 +4319,10 @@
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G13" s="6">
         <v>13000000</v>
@@ -4279,16 +4334,18 @@
       <c r="J13" s="4"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
+      <c r="B14" s="15">
+        <v>4</v>
+      </c>
       <c r="C14" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D14" s="5"/>
       <c r="E14" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="G14" s="6">
         <v>2800000</v>
@@ -4304,10 +4361,10 @@
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="G15" s="6">
         <v>825000</v>
@@ -4319,16 +4376,18 @@
       <c r="J15" s="4"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
+      <c r="B16" s="15">
+        <v>5</v>
+      </c>
       <c r="C16" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="G16" s="6">
         <v>850000</v>
@@ -4347,7 +4406,7 @@
         <v>162</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G17" s="6">
         <v>3700000</v>
@@ -4359,16 +4418,18 @@
       <c r="J17" s="4"/>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B18" s="15"/>
+      <c r="B18" s="15">
+        <v>6</v>
+      </c>
       <c r="C18" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D18" s="5"/>
       <c r="E18" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="G18" s="6">
         <v>2245000</v>
@@ -4384,10 +4445,10 @@
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
       <c r="E19" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="G19" s="6">
         <v>100000</v>
@@ -4399,14 +4460,18 @@
       <c r="J19" s="4"/>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B20" s="15"/>
-      <c r="C20" s="5"/>
+      <c r="B20" s="15">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>254</v>
+      </c>
       <c r="D20" s="5"/>
       <c r="E20" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>242</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>243</v>
       </c>
       <c r="G20" s="6">
         <v>170000</v>
@@ -4422,10 +4487,10 @@
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>245</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>246</v>
       </c>
       <c r="G21" s="6">
         <v>1725000</v>
@@ -4441,10 +4506,10 @@
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>248</v>
       </c>
       <c r="G22" s="6">
         <v>2250000</v>
@@ -4460,10 +4525,10 @@
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G23" s="6">
         <v>2250000</v>
@@ -4475,13 +4540,25 @@
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B24" s="15"/>
-      <c r="C24" s="5"/>
+      <c r="B24" s="15">
+        <v>8</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>255</v>
+      </c>
       <c r="D24" s="5"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="4"/>
+      <c r="E24" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G24" s="6">
+        <v>100000</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
     </row>
@@ -4489,60 +4566,102 @@
       <c r="B25" s="15"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="4"/>
+      <c r="E25" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G25" s="6">
+        <v>100000</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B26" s="15">
-        <v>3</v>
-      </c>
+      <c r="B26" s="15"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="4"/>
+      <c r="E26" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="G26" s="6">
+        <v>100000</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B27" s="15"/>
-      <c r="C27" s="5"/>
+      <c r="B27" s="15">
+        <v>9</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>256</v>
+      </c>
       <c r="D27" s="5"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="4"/>
+      <c r="E27" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G27" s="6">
+        <v>899000</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15">
-        <v>4</v>
-      </c>
-      <c r="C28" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>257</v>
+      </c>
       <c r="D28" s="5"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="4"/>
+      <c r="E28" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G28" s="6">
+        <v>2950000</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="15">
-        <v>5</v>
-      </c>
+      <c r="B29" s="15"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="4"/>
+      <c r="E29" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G29" s="6">
+        <v>13180000</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
     </row>
@@ -4550,23 +4669,35 @@
       <c r="B30" s="15"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
-      <c r="E30" s="4"/>
+      <c r="E30" s="4" t="s">
+        <v>89</v>
+      </c>
       <c r="F30" s="4"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="4"/>
+      <c r="G30" s="6">
+        <v>275000</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="15">
-        <v>6</v>
-      </c>
+    <row r="31" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="15"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="4"/>
+      <c r="E31" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G31" s="6">
+        <v>575000</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
     </row>
@@ -4574,10 +4705,18 @@
       <c r="B32" s="15"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="G32" s="6">
+        <v>850000</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
     </row>
@@ -4585,36 +4724,51 @@
       <c r="B33" s="15"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="4"/>
+      <c r="E33" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="G33" s="6">
+        <v>8175000</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>102</v>
+      </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15">
-        <v>7</v>
-      </c>
-      <c r="C34" s="5"/>
+        <v>11</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>264</v>
+      </c>
       <c r="D34" s="5"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G34" s="6">
+        <v>777000</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B35" s="15">
-        <v>8</v>
-      </c>
+      <c r="B35" s="15"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="6"/>
-      <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
@@ -4630,9 +4784,7 @@
       <c r="J36" s="4"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B37" s="15">
-        <v>9</v>
-      </c>
+      <c r="B37" s="15"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="4"/>
@@ -4687,9 +4839,7 @@
       <c r="J41" s="4"/>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B42" s="15">
-        <v>10</v>
-      </c>
+      <c r="B42" s="15"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="4"/>
@@ -4711,9 +4861,7 @@
       <c r="J43" s="4"/>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B44" s="15">
-        <v>11</v>
-      </c>
+      <c r="B44" s="15"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
       <c r="E44" s="4"/>
@@ -4724,9 +4872,7 @@
       <c r="J44" s="4"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B45" s="15">
-        <v>12</v>
-      </c>
+      <c r="B45" s="15"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="4"/>
@@ -4737,9 +4883,7 @@
       <c r="J45" s="4"/>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="15">
-        <v>13</v>
-      </c>
+      <c r="B46" s="15"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="4"/>
@@ -4750,9 +4894,7 @@
       <c r="J46" s="4"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="15">
-        <v>14</v>
-      </c>
+      <c r="B47" s="15"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="4"/>
@@ -4774,9 +4916,7 @@
       <c r="J48" s="4"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="15">
-        <v>15</v>
-      </c>
+      <c r="B49" s="15"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="4"/>
@@ -4798,9 +4938,7 @@
       <c r="J50" s="4"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B51" s="15">
-        <v>16</v>
-      </c>
+      <c r="B51" s="15"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="4"/>
@@ -4833,9 +4971,7 @@
       <c r="J53" s="4"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B54" s="15">
-        <v>17</v>
-      </c>
+      <c r="B54" s="15"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="4"/>
@@ -4846,9 +4982,7 @@
       <c r="J54" s="4"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B55" s="15">
-        <v>18</v>
-      </c>
+      <c r="B55" s="15"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="4"/>
@@ -4892,9 +5026,7 @@
       <c r="J58" s="4"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B59" s="15">
-        <v>19</v>
-      </c>
+      <c r="B59" s="15"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="4"/>
@@ -4908,15 +5040,9 @@
       <c r="B60" s="15"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
-      <c r="E60" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>205</v>
-      </c>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="6"/>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
@@ -5034,7 +5160,7 @@
     <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G71" s="16">
         <f>SUM(G5:G70)</f>
-        <v>56167000</v>
+        <v>84148000</v>
       </c>
     </row>
   </sheetData>
@@ -5043,7 +5169,7 @@
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="H5:H70">
+  <conditionalFormatting sqref="H36:H70 H5:H34">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
@@ -5055,11 +5181,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H70" xr:uid="{D40D73DF-17D8-4369-B0DF-04510FA59EB8}">
-      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I70" xr:uid="{B03ED550-A901-4976-BC2F-1D6468F9DB7D}">
       <formula1>"TUNAI,TRANSFER"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36:H70 H5:H34" xr:uid="{D40D73DF-17D8-4369-B0DF-04510FA59EB8}">
+      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Tagihan/REKAP TAGIHAN 2026.xlsx
+++ b/Tagihan/REKAP TAGIHAN 2026.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Data-Pekerjaan\Tagihan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CDBFA032-7CBD-4BFB-8C27-F931DBC84DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C2A426-FBC7-4FA6-9B6F-80597B175DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="598" activeTab="2" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="598" activeTab="3" xr2:uid="{BDEDF47B-1279-4C7F-95B0-1DB6A955F9DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Juli" sheetId="1" r:id="rId1"/>
     <sheet name="Agustus" sheetId="2" r:id="rId2"/>
     <sheet name="September" sheetId="3" r:id="rId3"/>
+    <sheet name="Oktober" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="319">
   <si>
     <t>No</t>
   </si>
@@ -839,6 +840,162 @@
   </si>
   <si>
     <t>1 Paket Imou PS8E 3mp</t>
+  </si>
+  <si>
+    <t>21 September 2026</t>
+  </si>
+  <si>
+    <t>MM Food Court</t>
+  </si>
+  <si>
+    <t>Kejaksaan</t>
+  </si>
+  <si>
+    <t>Perbaikan Kamera CCTV</t>
+  </si>
+  <si>
+    <t>Perbaikan Laptop</t>
+  </si>
+  <si>
+    <t>Habibi</t>
+  </si>
+  <si>
+    <t>22 September 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camelia </t>
+  </si>
+  <si>
+    <t>Tambah Kamera</t>
+  </si>
+  <si>
+    <t>Perkim</t>
+  </si>
+  <si>
+    <t>Perbaikan Kamera</t>
+  </si>
+  <si>
+    <t>Pasang Lampu Strip</t>
+  </si>
+  <si>
+    <t>Kambitin (Mba Dewi)</t>
+  </si>
+  <si>
+    <t>Paket 4 Kamera Proview</t>
+  </si>
+  <si>
+    <t>Klinik Olive</t>
+  </si>
+  <si>
+    <t>Acha mart</t>
+  </si>
+  <si>
+    <t>Service AC dan Pasang Rak</t>
+  </si>
+  <si>
+    <t>Adaptor 12V 5A</t>
+  </si>
+  <si>
+    <t>23 September 2026</t>
+  </si>
+  <si>
+    <t>24 September 2026</t>
+  </si>
+  <si>
+    <t>Pemasangan TV Polytron</t>
+  </si>
+  <si>
+    <t>Pa Remon</t>
+  </si>
+  <si>
+    <t>Pemasangan Speaker</t>
+  </si>
+  <si>
+    <t>Paket Ezviz TY1 Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gumuk </t>
+  </si>
+  <si>
+    <t>Pengambilan Barang Dvr,Psu dan Harddisk</t>
+  </si>
+  <si>
+    <t>Pengambilan Ezviz H8c 2mp dan Poe splitter (12 pcs)</t>
+  </si>
+  <si>
+    <t>01 Oktober 2026</t>
+  </si>
+  <si>
+    <t>Tambah Kamera baru 6 Unit</t>
+  </si>
+  <si>
+    <t>SDN 2 Mabuun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tambah CCTV Baru </t>
+  </si>
+  <si>
+    <t>H Surian</t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV (Kamera mati)</t>
+  </si>
+  <si>
+    <t>Sinar Tani</t>
+  </si>
+  <si>
+    <t>CCTV Offline</t>
+  </si>
+  <si>
+    <t>30 September 2026</t>
+  </si>
+  <si>
+    <t>28 September 2026</t>
+  </si>
+  <si>
+    <t>29 September 2026</t>
+  </si>
+  <si>
+    <t>03 Oktober 2026</t>
+  </si>
+  <si>
+    <t>PMI</t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV (mati 3 kamera)</t>
+  </si>
+  <si>
+    <t>Kamera Buram dan Tarik Kabel LAN</t>
+  </si>
+  <si>
+    <t>Ading H Jani</t>
+  </si>
+  <si>
+    <t>2 Paket Ezviz dan Perbaikan CCTV Lama</t>
+  </si>
+  <si>
+    <t>SLP Batu Kajang</t>
+  </si>
+  <si>
+    <t>Pemasangan CCTV 16 Kamera</t>
+  </si>
+  <si>
+    <t>Perbaikan Kabel Lan yang Putus</t>
+  </si>
+  <si>
+    <t>Bapak Cepot</t>
+  </si>
+  <si>
+    <t>05 Oktober 2026</t>
+  </si>
+  <si>
+    <t>Sei Pimping</t>
+  </si>
+  <si>
+    <t>1 Paket Kamera ezviz H8c 2mp</t>
+  </si>
+  <si>
+    <t>Perbaikan CCTV dan Service AC</t>
   </si>
 </sst>
 </file>
@@ -848,7 +1005,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -884,8 +1041,13 @@
       <charset val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -907,6 +1069,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -938,7 +1106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -979,6 +1147,7 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -989,7 +1158,28 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1385,17 +1575,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -1426,13 +1616,13 @@
         <v>6</v>
       </c>
       <c r="L4" s="13"/>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
@@ -2645,13 +2835,13 @@
     <mergeCell ref="B2:J2"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H59">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="DIBAYAR">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="DITAGIH">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="DITAGIH">
       <formula>NOT(ISERROR(SEARCH("DITAGIH",H5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="DIBUAT">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="DIBUAT">
       <formula>NOT(ISERROR(SEARCH("DIBUAT",H5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2691,17 +2881,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -2732,13 +2922,13 @@
         <v>6</v>
       </c>
       <c r="L4" s="13"/>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
@@ -4004,13 +4194,13 @@
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H68">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="DIBAYAR">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="DITAGIH">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="DITAGIH">
       <formula>NOT(ISERROR(SEARCH("DITAGIH",H5)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="DIBUAT">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="DIBUAT">
       <formula>NOT(ISERROR(SEARCH("DIBUAT",H5)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4051,17 +4241,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
@@ -4092,13 +4282,13 @@
         <v>6</v>
       </c>
       <c r="L4" s="13"/>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="15">
@@ -4672,7 +4862,9 @@
       <c r="E30" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F30" s="4"/>
+      <c r="F30" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="G30" s="6">
         <v>275000</v>
       </c>
@@ -4682,18 +4874,18 @@
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
     </row>
-    <row r="31" spans="2:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="G31" s="6">
-        <v>575000</v>
+        <v>850000</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>12</v>
@@ -4706,17 +4898,1217 @@
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="G32" s="6">
+        <v>8175000</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="15">
+        <v>11</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="D33" s="5"/>
+      <c r="E33" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G33" s="6">
+        <v>777000</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="15">
+        <v>12</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="D34" s="5"/>
+      <c r="E34" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G34" s="6">
+        <v>196000</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="15"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="G35" s="6">
+        <v>580000</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="15"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G36" s="6">
+        <v>650000</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="15">
+        <v>13</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="D37" s="5"/>
+      <c r="E37" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G37" s="6">
+        <v>150000</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="15"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="G38" s="6">
+        <v>3515000</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="15"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G39" s="6">
+        <v>650000</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="15"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G40" s="6">
+        <v>2835000</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="15">
+        <v>14</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="E41" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="G41" s="6">
+        <v>4765000</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="15"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="G42" s="6">
+        <v>3950000</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="15"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="G43" s="6">
+        <v>250000</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="15">
+        <v>15</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="E44" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G44" s="6">
+        <v>1675000</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="15"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G45" s="6">
+        <v>250000</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="15"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="G32" s="6">
+      <c r="F46" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G46" s="6">
+        <v>250000</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="15"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="G47" s="6">
+        <v>7340000</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="15">
+        <v>16</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="G48" s="6">
+        <v>5080000</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="15"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="G49" s="6">
+        <v>12853000</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="15"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G50" s="6">
         <v>850000</v>
       </c>
-      <c r="H32" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="H50" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="15"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1650000</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="15"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="15">
+        <v>17</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="E53" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G53" s="6">
+        <v>275000</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="15"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G54" s="6">
+        <v>195000</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B55" s="15"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="G55" s="6">
+        <v>190000</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="15"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G56" s="6">
+        <v>200000</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="15">
+        <v>18</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D57" s="5"/>
+      <c r="E57" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G57" s="6">
+        <v>1265000</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="15"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="15"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="15"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B61" s="15"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="15"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="15"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="15"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B65" s="15"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B66" s="15"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B67" s="15"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B68" s="15"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B69" s="15"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B70" s="15"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G71" s="16">
+        <f>SUM(G5:G70)</f>
+        <v>133187000</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:J2"/>
+    <mergeCell ref="M4:Q4"/>
+  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="H5:H70">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="DIBAYAR">
+      <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="DITAGIH">
+      <formula>NOT(ISERROR(SEARCH("DITAGIH",H5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="DIBUAT">
+      <formula>NOT(ISERROR(SEARCH("DIBUAT",H5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I70" xr:uid="{B03ED550-A901-4976-BC2F-1D6468F9DB7D}">
+      <formula1>"TUNAI,TRANSFER"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H70" xr:uid="{D40D73DF-17D8-4369-B0DF-04510FA59EB8}">
+      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D743939B-851E-445D-9553-B16A266BF0DD}">
+  <dimension ref="B2:Q70"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="4.5703125" style="14" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="39.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="35.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="74.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="27.42578125" style="3" customWidth="1"/>
+    <col min="8" max="9" width="22" style="1" customWidth="1"/>
+    <col min="10" max="10" width="51.42578125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
+    <col min="12" max="12" width="3.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="1.42578125" style="1" customWidth="1"/>
+    <col min="15" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="3.5703125" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:17" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="B2" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+    </row>
+    <row r="4" spans="2:17" s="12" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="13"/>
+      <c r="M4" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="23"/>
+      <c r="Q4" s="23"/>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B5" s="15">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="G5" s="6">
+        <v>7630000</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B6" s="15"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="6">
+        <v>250000</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B7" s="15"/>
+      <c r="C7" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="G7" s="6">
+        <v>495000</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B8" s="15"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G8" s="6">
+        <v>275000</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B9" s="15"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G9" s="6">
+        <v>2980000</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B10" s="15"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G10" s="6">
+        <v>10355000</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B11" s="15"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="G11" s="6">
+        <v>230000</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B12" s="15"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G12" s="6">
+        <v>100000</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+    </row>
+    <row r="13" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="15"/>
+      <c r="C13" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1150000</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B14" s="15"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="G14" s="6">
+        <v>470000</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+    </row>
+    <row r="15" spans="2:17" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="15"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B16" s="15"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="15"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="15"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="15"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="15"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="15"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="15"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="15"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="15"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="15"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="15"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="15"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="15"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="15"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="15"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="4"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="15"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="4"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="15"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
     </row>
@@ -4724,41 +6116,21 @@
       <c r="B33" s="15"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
-      <c r="E33" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="G33" s="6">
-        <v>8175000</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>102</v>
-      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="4"/>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="15">
-        <v>11</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>264</v>
-      </c>
+      <c r="B34" s="15"/>
+      <c r="C34" s="5"/>
       <c r="D34" s="5"/>
-      <c r="E34" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="G34" s="6">
-        <v>777000</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
     </row>
@@ -4769,6 +6141,7 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="6"/>
+      <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
     </row>
@@ -5147,20 +6520,9 @@
       <c r="J69" s="4"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B70" s="15"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G71" s="16">
-        <f>SUM(G5:G70)</f>
-        <v>84148000</v>
+      <c r="G70" s="16">
+        <f>SUM(G5:G69)</f>
+        <v>23935000</v>
       </c>
     </row>
   </sheetData>
@@ -5168,8 +6530,7 @@
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="M4:Q4"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="H36:H70 H5:H34">
+  <conditionalFormatting sqref="H5:H69">
     <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="DIBAYAR">
       <formula>NOT(ISERROR(SEARCH("DIBAYAR",H5)))</formula>
     </cfRule>
@@ -5181,11 +6542,11 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I70" xr:uid="{B03ED550-A901-4976-BC2F-1D6468F9DB7D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H69" xr:uid="{F27D2EAF-9882-406E-85C2-6A886EEA21C4}">
+      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I5:I69" xr:uid="{5A45ABA8-B1ED-4E77-95F2-17AE4D6480DA}">
       <formula1>"TUNAI,TRANSFER"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H36:H70 H5:H34" xr:uid="{D40D73DF-17D8-4369-B0DF-04510FA59EB8}">
-      <formula1>"DIBUAT,DITAGIH,DIBAYAR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
